--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486864_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486864_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2528</v>
+        <v>3.4306</v>
       </c>
       <c r="E2" t="n">
         <v>4.7356</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4828</v>
+        <v>-1.3049</v>
       </c>
       <c r="G2" t="n">
         <v>3.8223</v>
@@ -610,13 +610,13 @@
         <v>2.4641</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.466</v>
+        <v>-1.2882</v>
       </c>
       <c r="T2" t="n">
         <v>-0.5465</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9195</v>
+        <v>-0.7417</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3356</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1912</v>
+        <v>1.6106</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0059</v>
+        <v>2.6921</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8148</v>
+        <v>-1.0816</v>
       </c>
       <c r="G3" t="n">
         <v>1.0839</v>
@@ -688,13 +688,13 @@
         <v>1.8481</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1856</v>
+        <v>-0.7662</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4879</v>
+        <v>0.1741</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6735</v>
+        <v>-0.9403</v>
       </c>
       <c r="V3" t="n">
         <v>0.4715</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1149</v>
+        <v>-0.511</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6329</v>
+        <v>0.2145</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.518</v>
+        <v>-0.7255</v>
       </c>
       <c r="G4" t="n">
         <v>2.1214</v>
@@ -766,13 +766,13 @@
         <v>0.2053</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4391</v>
+        <v>-0.1868</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1704</v>
+        <v>-0.248</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2687</v>
+        <v>0.0612</v>
       </c>
       <c r="V4" t="n">
         <v>-1.4189</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. REID</t>
+          <t>F. ANDRADE AMIEL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.4972</v>
+        <v>-1.3106</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2987</v>
+        <v>-2.9625</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.796</v>
+        <v>1.6519</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.1074</v>
+        <v>-0.7573</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4345</v>
+        <v>0.4347</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5418</v>
+        <v>-1.192</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5435</v>
+        <v>-1.1182</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6492</v>
+        <v>0.237</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1057</v>
+        <v>-1.3552</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6509</v>
+        <v>0.3609</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2147</v>
+        <v>0.1977</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4361</v>
+        <v>0.1632</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0534</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2053</v>
+        <v>-2.0534</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2588</v>
+        <v>0.616</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2782</v>
+        <v>-0.2945</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1708</v>
+        <v>-0.2713</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.1074</v>
+        <v>-0.0232</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1651</v>
+        <v>1.1786</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1314</v>
+        <v>0.4805</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2965</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. ANDRADE AMIEL</t>
+          <t>N. REID</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.8615</v>
+        <v>-1.7814</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.2763</v>
+        <v>-0.0151</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4148</v>
+        <v>-1.7663</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7573</v>
+        <v>-1.1074</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4347</v>
+        <v>0.4345</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.192</v>
+        <v>-1.5418</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.1182</v>
+        <v>0.5435</v>
       </c>
       <c r="K6" t="n">
-        <v>0.237</v>
+        <v>0.6492</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3552</v>
+        <v>-0.1057</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3609</v>
+        <v>-1.6509</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1977</v>
+        <v>-0.2147</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1632</v>
+        <v>-1.4361</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.4374</v>
+        <v>2.0534</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0534</v>
+        <v>-0.2053</v>
       </c>
       <c r="R6" t="n">
-        <v>0.616</v>
+        <v>2.2588</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8454</v>
+        <v>-1.5623</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5851</v>
+        <v>-0.4846</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2603</v>
+        <v>-1.0778</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1786</v>
+        <v>-1.1651</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4805</v>
+        <v>0.1314</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6982</v>
+        <v>-1.2965</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1573</v>
+        <v>-2.2166</v>
       </c>
       <c r="E7" t="n">
         <v>2.1459</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.3032</v>
+        <v>-4.3625</v>
       </c>
       <c r="G7" t="n">
         <v>0.2178</v>
@@ -1000,13 +1000,13 @@
         <v>2.0534</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5078</v>
+        <v>-1.5671</v>
       </c>
       <c r="T7" t="n">
         <v>-0.4806</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0272</v>
+        <v>-1.0865</v>
       </c>
       <c r="V7" t="n">
         <v>-2.7154</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. BRAMBLE</t>
+          <t>V. AGUILAR HERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4477</v>
+        <v>-2.664</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9056999999999999</v>
+        <v>-3.573</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5419</v>
+        <v>0.909</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4856</v>
+        <v>-1.7664</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3405</v>
+        <v>1.5541</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-3.3205</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0823</v>
+        <v>-0.8414</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0034</v>
+        <v>1.1587</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0789</v>
+        <v>-2.0001</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5679</v>
+        <v>-0.9251</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3371</v>
+        <v>0.3953</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.905</v>
+        <v>-1.3204</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2053</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0267</v>
+        <v>-2.2588</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2321</v>
+        <v>2.0534</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5084</v>
+        <v>-0.8146</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0386</v>
+        <v>-0.7131</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.547</v>
+        <v>-0.1015</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.6591</v>
+        <v>0.1224</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.6591</v>
+        <v>-0.1179</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. AGUILAR HERNANDEZ</t>
+          <t>O. BRAMBLE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2166</v>
+        <v>-2.9254</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.096</v>
+        <v>-1.3241</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8794</v>
+        <v>-1.6012</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7664</v>
+        <v>-0.4856</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5541</v>
+        <v>0.3405</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.3205</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8414</v>
+        <v>0.0823</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1587</v>
+        <v>0.0034</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.0001</v>
+        <v>0.0789</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9251</v>
+        <v>-0.5679</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3953</v>
+        <v>0.3371</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3204</v>
+        <v>-0.905</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2053</v>
+        <v>0.2053</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2588</v>
+        <v>-1.0267</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0534</v>
+        <v>1.2321</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3672</v>
+        <v>-0.986</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2361</v>
+        <v>-0.3798</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1311</v>
+        <v>-0.6063</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1224</v>
+        <v>-1.6591</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1179</v>
+        <v>-1.6591</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.5961</v>
+        <v>-3.8499</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3197</v>
+        <v>-1.6921</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2764</v>
+        <v>-2.1578</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0247</v>
@@ -1234,13 +1234,13 @@
         <v>0.616</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5714</v>
+        <v>-0.8252</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9145</v>
+        <v>-0.2869</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6569</v>
+        <v>-0.5384</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5893</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.2175</v>
+        <v>-10.2177</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2213000000000003</v>
+        <v>0.2213000000000007</v>
       </c>
       <c r="F11" t="n">
         <v>-10.4389</v>
@@ -1291,7 +1291,7 @@
         <v>8.438599999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>3.9313</v>
+        <v>3.931299999999999</v>
       </c>
       <c r="M11" t="n">
         <v>-11.2661</v>
@@ -1318,7 +1318,7 @@
         <v>-3.2367</v>
       </c>
       <c r="U11" t="n">
-        <v>-5.0542</v>
+        <v>-5.0545</v>
       </c>
       <c r="V11" t="n">
         <v>-6.110899999999999</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. LOPEZ-SANVICENTE RETA</t>
+          <t>G. VAZQUEZ VALLEJO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.1765</v>
+        <v>4.4838</v>
       </c>
       <c r="E12" t="n">
-        <v>1.1304</v>
+        <v>3.9498</v>
       </c>
       <c r="F12" t="n">
-        <v>3.0461</v>
+        <v>0.534</v>
       </c>
       <c r="G12" t="n">
-        <v>1.9049</v>
+        <v>2.4099</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7417</v>
+        <v>-1.6448</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1632</v>
+        <v>4.0546</v>
       </c>
       <c r="J12" t="n">
-        <v>1.6882</v>
+        <v>4.2638</v>
       </c>
       <c r="K12" t="n">
-        <v>1.5962</v>
+        <v>-0.0905</v>
       </c>
       <c r="L12" t="n">
-        <v>0.092</v>
+        <v>4.3543</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2167</v>
+        <v>-1.8539</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1455</v>
+        <v>-1.5543</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0713</v>
+        <v>-0.2996</v>
       </c>
       <c r="P12" t="n">
+        <v>-0.4107</v>
+      </c>
+      <c r="Q12" t="n">
         <v>-1.0267</v>
       </c>
-      <c r="Q12" t="n">
-        <v>-2.0534</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.0267</v>
+        <v>0.616</v>
       </c>
       <c r="S12" t="n">
-        <v>2.9493</v>
+        <v>1.6776</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9064</v>
+        <v>0.7127</v>
       </c>
       <c r="U12" t="n">
-        <v>2.0429</v>
+        <v>0.9649</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3491</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2402</v>
+        <v>0.8070000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. VAZQUEZ VALLEJO</t>
+          <t>P. LOPEZ-SANVICENTE RETA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.9678</v>
+        <v>2.9979</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2175</v>
+        <v>0.5028</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7503</v>
+        <v>2.4951</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4099</v>
+        <v>1.9049</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.6448</v>
+        <v>1.7417</v>
       </c>
       <c r="I13" t="n">
-        <v>4.0546</v>
+        <v>0.1632</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2638</v>
+        <v>1.6882</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.0905</v>
+        <v>1.5962</v>
       </c>
       <c r="L13" t="n">
-        <v>4.3543</v>
+        <v>0.092</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.8539</v>
+        <v>0.2167</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5543</v>
+        <v>0.1455</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2996</v>
+        <v>0.0713</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.4107</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R13" t="n">
-        <v>0.616</v>
+        <v>1.0267</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1616</v>
+        <v>1.7706</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0195</v>
+        <v>0.2787</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1811</v>
+        <v>1.4919</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.3491</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8070000000000001</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4033</v>
+        <v>2.6875</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5134</v>
+        <v>3.8272</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1101</v>
+        <v>-1.1397</v>
       </c>
       <c r="G14" t="n">
         <v>-0.3448</v>
@@ -1546,13 +1546,13 @@
         <v>1.0267</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3251</v>
+        <v>0.6092</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3834</v>
+        <v>0.6973</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0584</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>1.3963</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3965</v>
+        <v>2.2379</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8416</v>
+        <v>0.6323</v>
       </c>
       <c r="F15" t="n">
-        <v>1.555</v>
+        <v>1.6055</v>
       </c>
       <c r="G15" t="n">
         <v>2.0381</v>
@@ -1624,13 +1624,13 @@
         <v>1.2321</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0914</v>
+        <v>0.9328</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3408</v>
+        <v>0.1315</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7507</v>
+        <v>0.8012</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9384</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3928</v>
+        <v>1.351</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9255</v>
+        <v>1.507</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5326</v>
+        <v>-0.156</v>
       </c>
       <c r="G16" t="n">
         <v>-1.1255</v>
@@ -1702,13 +1702,13 @@
         <v>1.8481</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3048</v>
+        <v>1.263</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9954</v>
+        <v>0.577</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3093</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>1.4189</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9054</v>
+        <v>0.7624</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9973</v>
+        <v>2.8927</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0919</v>
+        <v>-2.1302</v>
       </c>
       <c r="G17" t="n">
         <v>-2.778</v>
@@ -1780,13 +1780,13 @@
         <v>0.8214</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4002</v>
+        <v>1.2572</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0885</v>
+        <v>0.9839</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3116</v>
+        <v>0.2732</v>
       </c>
       <c r="V17" t="n">
         <v>2.4886</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. RUBIN DE CELIS FERRANDO</t>
+          <t>H. FIGUEROA ÁLVAREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4513</v>
+        <v>0.7107</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.3609</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5436</v>
+        <v>1.0717</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.829</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1.2293</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5973000000000001</v>
+        <v>-0.4004</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0395</v>
+        <v>1.1464</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1.5023</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0395</v>
+        <v>-0.3559</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5579</v>
+        <v>-0.3174</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.2729</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5579</v>
+        <v>-0.0445</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2053</v>
+        <v>-0.616</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2053</v>
+        <v>1.4374</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3514</v>
+        <v>0.4978</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1317</v>
+        <v>0.3059</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2197</v>
+        <v>0.1919</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H. FIGUEROA ÁLVAREZ</t>
+          <t>A. RUBIN DE CELIS FERRANDO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6248</v>
+        <v>0.5402</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.884</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2592</v>
+        <v>0.6325</v>
       </c>
       <c r="G19" t="n">
-        <v>0.829</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2293</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4004</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1464</v>
+        <v>0.0395</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5023</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3559</v>
+        <v>0.0395</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3174</v>
+        <v>0.5579</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2729</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0445</v>
+        <v>0.5579</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4374</v>
+        <v>0.2053</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8377</v>
+        <v>-0.2625</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2171</v>
+        <v>-0.1317</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6206</v>
+        <v>-0.1307</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.988</v>
+        <v>-0.7491</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5579</v>
+        <v>-0.3487</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4301</v>
+        <v>-0.4004</v>
       </c>
       <c r="G20" t="n">
         <v>-1.0077</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0198</v>
+        <v>0.2586</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1395</v>
+        <v>0.3487</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1197</v>
+        <v>-0.0901</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. CARREIRA KREPS</t>
+          <t>J. WELLS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7139</v>
+        <v>-1.6979</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1395</v>
+        <v>0.5916</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4256</v>
+        <v>-2.2895</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7072000000000001</v>
+        <v>-2.92</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0835</v>
+        <v>-2.5012</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3763</v>
+        <v>-0.4188</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.337</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="K21" t="n">
         <v>-1.0604</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7234</v>
+        <v>0.9729</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3702</v>
+        <v>-2.8325</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0231</v>
+        <v>-1.4409</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3472</v>
+        <v>-1.3917</v>
       </c>
       <c r="P21" t="n">
         <v>-1.0267</v>
@@ -2092,28 +2092,28 @@
         <v>1.0267</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3691</v>
+        <v>1.3104</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5799</v>
+        <v>0.5861</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3491</v>
+        <v>0.9384</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6982</v>
+        <v>2.0082</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3491</v>
+        <v>-1.0698</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. WELLS</t>
+          <t>M. CARREIRA KREPS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,40 +2125,40 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1495</v>
+        <v>-1.712</v>
       </c>
       <c r="E22" t="n">
-        <v>0.487</v>
+        <v>-2.6625</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6364</v>
+        <v>0.9505</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.92</v>
+        <v>-0.7072000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.5012</v>
+        <v>-1.0835</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4188</v>
+        <v>0.3763</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.337</v>
       </c>
       <c r="K22" t="n">
         <v>-1.0604</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9729</v>
+        <v>0.7234</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.8325</v>
+        <v>-0.3702</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4409</v>
+        <v>-0.0231</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3917</v>
+        <v>-0.3472</v>
       </c>
       <c r="P22" t="n">
         <v>-1.0267</v>
@@ -2170,22 +2170,22 @@
         <v>1.0267</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8589</v>
+        <v>0.3709</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6197</v>
+        <v>0.426</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2392</v>
+        <v>-0.0551</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9384</v>
+        <v>-0.3491</v>
       </c>
       <c r="W22" t="n">
-        <v>2.0082</v>
+        <v>-0.6982</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0698</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>10.2174</v>
+        <v>11.6124</v>
       </c>
       <c r="E23" t="n">
         <v>10.439</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2213000000000003</v>
+        <v>1.1735</v>
       </c>
       <c r="G23" t="n">
         <v>-1.104000000000001</v>
@@ -2233,7 +2233,7 @@
         <v>-12.37</v>
       </c>
       <c r="N23" t="n">
-        <v>-8.438600000000001</v>
+        <v>-8.438599999999999</v>
       </c>
       <c r="O23" t="n">
         <v>-3.9314</v>
@@ -2248,13 +2248,13 @@
         <v>10.2671</v>
       </c>
       <c r="S23" t="n">
-        <v>8.2911</v>
+        <v>9.685599999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>5.054499999999999</v>
+        <v>5.0543</v>
       </c>
       <c r="U23" t="n">
-        <v>3.2365</v>
+        <v>4.6313</v>
       </c>
       <c r="V23" t="n">
         <v>6.110799999999999</v>
